--- a/artfynd/A 33279-2021 artfynd.xlsx
+++ b/artfynd/A 33279-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33279-2021 artfynd.xlsx
+++ b/artfynd/A 33279-2021 artfynd.xlsx
@@ -9224,7 +9224,7 @@
         <v>131738798</v>
       </c>
       <c r="B68" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>131739569</v>
       </c>
       <c r="B69" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9423,32 +9423,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131732376</v>
+        <v>131738069</v>
       </c>
       <c r="B70" t="n">
-        <v>96403</v>
+        <v>80422</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>653226</v>
+        <v>653248</v>
       </c>
       <c r="R70" t="n">
-        <v>6647894</v>
+        <v>6647981</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9524,32 +9524,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131738069</v>
+        <v>131732376</v>
       </c>
       <c r="B71" t="n">
-        <v>80420</v>
+        <v>96406</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>653248</v>
+        <v>653226</v>
       </c>
       <c r="R71" t="n">
-        <v>6647981</v>
+        <v>6647894</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 33279-2021 artfynd.xlsx
+++ b/artfynd/A 33279-2021 artfynd.xlsx
@@ -9423,32 +9423,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131738069</v>
+        <v>131732376</v>
       </c>
       <c r="B70" t="n">
-        <v>80422</v>
+        <v>96406</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>653248</v>
+        <v>653226</v>
       </c>
       <c r="R70" t="n">
-        <v>6647981</v>
+        <v>6647894</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9524,32 +9524,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131732376</v>
+        <v>131738069</v>
       </c>
       <c r="B71" t="n">
-        <v>96406</v>
+        <v>80422</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2671</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>653226</v>
+        <v>653248</v>
       </c>
       <c r="R71" t="n">
-        <v>6647894</v>
+        <v>6647981</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
